--- a/innovation/model/Counterweight-Model.xlsx
+++ b/innovation/model/Counterweight-Model.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>[ASSUMPTION] Inference plus infrastructure. Not measured. The dial most likely to be wrong.</t>
+          <t>COSTED at ~$18.50/customer (2026-08-31). Kept at 45 deliberately as headroom, because flat pricing absorbs heavy users.</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>[ASSUMPTION] Cost to serve, $45/customer/month. Not measured. Flat pricing means a heavy user is absorbed, so a fair-use ceiling belongs in the terms from day one. If this is really $120, gross margin falls from 85% to 60% and the model needs a higher price.</t>
+          <t>[REVIEW, costed 2026-08-31] Real cost to serve is about $18.50/customer/month at 100 customers: roughly $9 of model inference, $9 of Stripe, and about $0.47 of everything else. The dial is left at $45 as deliberate headroom, because flat pricing absorbs heavy users and a firm running thousand-page productions costs several times a light one. If the true figure were $120, gross margin would fall from 94% to 60% and the price would need to rise.</t>
         </is>
       </c>
     </row>
